--- a/Compititor's_Price/Mannok_Prices/Mannok_Prices_30-07-2025.xlsx
+++ b/Compititor's_Price/Mannok_Prices/Mannok_Prices_30-07-2025.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£16.70</t>
+          <t>£16.60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£16.70</t>
+          <t>£16.60</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£28.99</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£28.99</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
